--- a/etf_holdings/2026-09-03_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-03_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,97 +486,133 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.49%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1457000</v>
+      </c>
       <c r="K2" t="n">
-        <v>158000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>219000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-1,238,000</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-02_00990A_full_holdings.xlsx</t>
+          <t>2026-09-02_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>325000</v>
+      </c>
       <c r="K3" t="n">
-        <v>94000</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>372000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>47,000</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-02_00990A_full_holdings.xlsx</t>
+          <t>2026-09-02_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -591,55 +627,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>4.95%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1008000</v>
+        <v>2397000</v>
       </c>
       <c r="K4" t="n">
-        <v>1665000</v>
+        <v>2427000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>657,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-02_00990A_full_holdings.xlsx</t>
+          <t>2026-09-02_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -654,55 +690,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2045000</v>
+        <v>2838000</v>
       </c>
       <c r="K5" t="n">
-        <v>1000000</v>
+        <v>2184000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-1,045,000</t>
+          <t>-654,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -712,60 +748,60 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>55000</v>
+        <v>9474000</v>
       </c>
       <c r="K6" t="n">
-        <v>80000</v>
+        <v>9426000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>-48,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -775,123 +811,105 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>緯穎科技服務</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>緯穎科技服務</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>108000</v>
+        <v>52000</v>
       </c>
       <c r="K7" t="n">
-        <v>54000</v>
+        <v>155105</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-54,000</t>
+          <t>103,105</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>+0.14%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K8" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -906,55 +924,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>195000</v>
+        <v>3404000</v>
       </c>
       <c r="K9" t="n">
-        <v>581644</v>
+        <v>3704000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>386,644</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -969,48 +987,4170 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>6531</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>愛普*</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>愛普*</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.01%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1660000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-02_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>13000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>103000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-02_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.13%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1351000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1,350,000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2,800,000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>220000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>16000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-204,000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2.09%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2.39%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>+0.30%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>189500</v>
+      </c>
+      <c r="K16" t="n">
+        <v>210500</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>21,000</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>225000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>125,000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>850000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>650000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4.11%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4.16%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>56000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>167036</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>111,036</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-02_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>7.61%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6.69%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>235000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>205000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-02_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>28000</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>87000</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>11000</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>29000</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>41000</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>凱基金控</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>729000</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>永豐金控</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>566220</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>39000</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>33000</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>13000</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>+1.92%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>821000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1613000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>792,000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>4.04%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3.80%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>28000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1338000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1276000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-62,000</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>台達電子</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>台達電子</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>110000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>+0.20%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>78000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>161000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>83,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>202000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>167000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-35,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>8.39%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>7.98%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>363000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>341000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-22,000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>550000</v>
+      </c>
+      <c r="K43" t="n">
+        <v>629000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>79,000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2.21%</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1496000</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1262000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-234,000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2.89%</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>140000</v>
+      </c>
+      <c r="K45" t="n">
+        <v>138000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>524000</v>
+      </c>
+      <c r="K46" t="n">
+        <v>448000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-76,000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2.28%</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>+0.96%</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>113000</v>
+      </c>
+      <c r="K47" t="n">
+        <v>198000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>85,000</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>5.68%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>5.27%</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>106000</v>
+      </c>
+      <c r="K48" t="n">
+        <v>99000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>763000</v>
+      </c>
+      <c r="K49" t="n">
+        <v>684000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-79,000</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>59000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>131000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>72,000</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>4.18%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>5.56%</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>+1.38%</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>102000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>133000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>31,000</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>+1.11%</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>113000</v>
+      </c>
+      <c r="K52" t="n">
+        <v>315000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>202,000</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>439360</v>
+      </c>
+      <c r="K53" t="n">
+        <v>105360</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-334,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>+0.97%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>13000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>3.46%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-0.88%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>134000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>107000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-27,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>149000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>312000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>163,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>4.19%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-1.12%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>454000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>323000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-131,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>97000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>192000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>95,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>健鼎科技</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>健鼎科技</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>43000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>88000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>45,000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>37000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>46000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>弘塑科技</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>弘塑科技</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K61" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-0.27%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>304000</v>
+      </c>
+      <c r="K62" t="n">
+        <v>273000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-31,000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>+0.64%</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>611000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>939000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>328,000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>+0.44%</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>367000</v>
+      </c>
+      <c r="K64" t="n">
+        <v>556000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>189,000</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>29000</v>
+      </c>
+      <c r="K65" t="n">
+        <v>23000</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-6,000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>90000</v>
+      </c>
+      <c r="K66" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>+0.18%</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>177000</v>
+      </c>
+      <c r="K67" t="n">
+        <v>352000</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>175,000</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>+1.06%</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>171000</v>
+      </c>
+      <c r="K68" t="n">
+        <v>390000</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>219,000</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>73872</v>
+      </c>
+      <c r="K69" t="n">
+        <v>52872</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-21,000</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>+0.41%</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>102000</v>
+      </c>
+      <c r="K70" t="n">
+        <v>165000</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>63,000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>173000</v>
+      </c>
+      <c r="K71" t="n">
+        <v>368000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>195,000</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>5.92%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>4.14%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-1.78%</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>115000</v>
+      </c>
+      <c r="K72" t="n">
+        <v>80000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-35,000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>77000</v>
+      </c>
+      <c r="K73" t="n">
+        <v>163000</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>86,000</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2.63%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-0.80%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>249000</v>
+      </c>
+      <c r="K74" t="n">
+        <v>191000</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-58,000</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>45000</v>
+      </c>
+      <c r="K75" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>45,000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>47000</v>
+      </c>
+      <c r="K76" t="n">
+        <v>140191</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>93,191</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>216000</v>
+      </c>
+      <c r="K77" t="n">
+        <v>185000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-31,000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>67000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>35,000</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.98%</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.72%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>+0.74%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>221000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>351000</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>130,000</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>+0.59%</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>82000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-03_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-03_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1647,270 +1647,378 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
+        </is>
+      </c>
       <c r="J21" t="n">
-        <v>28000</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+        <v>2045000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-1,045,000</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>光寶科技</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
       <c r="J22" t="n">
-        <v>87000</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+        <v>55000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>80000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.57%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>11000</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+        <v>108000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>54000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-54,000</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>29000</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>志聖</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+          <t>5.72%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>5.87%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>41000</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+        <v>195000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>581644</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>386,644</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>凱基金控</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1.72%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>+0.74%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>729000</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+        <v>221000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>351000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1932,24 +2040,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>永豐金控</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>566220</v>
+        <v>28000</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1977,24 +2085,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>16000</v>
+        <v>87000</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2022,24 +2130,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>4000</v>
+        <v>11000</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2067,24 +2175,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>100000</v>
+        <v>29000</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2112,24 +2220,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>19000</v>
+        <v>41000</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2157,24 +2265,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>凱基金控</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>39000</v>
+        <v>729000</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2202,24 +2310,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>永豐金控</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>33000</v>
+        <v>566220</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2247,24 +2355,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>昇達科技</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2292,24 +2400,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>13000</v>
+        <v>4000</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2327,55 +2435,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.83%</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>3.75%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>+1.92%</t>
-        </is>
-      </c>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>821000</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1613000</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>792,000</t>
-        </is>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2390,55 +2480,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.04%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3.80%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
-        </is>
-      </c>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K37" t="n">
-        <v>28000</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
+        <v>19000</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2453,55 +2525,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.69%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>1.57%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-0.12%</t>
-        </is>
-      </c>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>1338000</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1276000</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>-62,000</t>
-        </is>
-      </c>
+        <v>39000</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2516,55 +2570,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>台達電子</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>台達電子</t>
-        </is>
-      </c>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>110000</v>
-      </c>
-      <c r="K39" t="n">
-        <v>114000</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
+        <v>33000</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2579,55 +2615,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>+0.20%</t>
-        </is>
-      </c>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>78000</v>
-      </c>
-      <c r="K40" t="n">
-        <v>161000</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>83,000</t>
-        </is>
-      </c>
+        <v>32000</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2642,55 +2660,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.09%</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0.88%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>202000</v>
-      </c>
-      <c r="K41" t="n">
-        <v>167000</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>-35,000</t>
-        </is>
-      </c>
+        <v>13000</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2710,48 +2710,48 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8.39%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>7.98%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>363000</v>
+        <v>821000</v>
       </c>
       <c r="K42" t="n">
-        <v>341000</v>
+        <v>1613000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-22,000</t>
+          <t>792,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2773,48 +2773,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>3.80%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>550000</v>
+        <v>30000</v>
       </c>
       <c r="K43" t="n">
-        <v>629000</v>
+        <v>28000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -2841,43 +2841,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1496000</v>
+        <v>1338000</v>
       </c>
       <c r="K44" t="n">
-        <v>1262000</v>
+        <v>1276000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-234,000</t>
+          <t>-62,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -2899,48 +2899,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>140000</v>
+        <v>110000</v>
       </c>
       <c r="K45" t="n">
-        <v>138000</v>
+        <v>114000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -2962,48 +2962,48 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>524000</v>
+        <v>78000</v>
       </c>
       <c r="K46" t="n">
-        <v>448000</v>
+        <v>161000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-76,000</t>
+          <t>83,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3025,48 +3025,48 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>113000</v>
+        <v>202000</v>
       </c>
       <c r="K47" t="n">
-        <v>198000</v>
+        <v>167000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3093,27 +3093,27 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>8.39%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5.27%</t>
+          <t>7.98%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3122,14 +3122,14 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>106000</v>
+        <v>363000</v>
       </c>
       <c r="K48" t="n">
-        <v>99000</v>
+        <v>341000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>-22,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3151,48 +3151,48 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>763000</v>
+        <v>550000</v>
       </c>
       <c r="K49" t="n">
-        <v>684000</v>
+        <v>629000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-79,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3214,48 +3214,48 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>59000</v>
+        <v>1496000</v>
       </c>
       <c r="K50" t="n">
-        <v>131000</v>
+        <v>1262000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>-234,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3277,48 +3277,48 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>102000</v>
+        <v>140000</v>
       </c>
       <c r="K51" t="n">
-        <v>133000</v>
+        <v>138000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3340,48 +3340,48 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>113000</v>
+        <v>524000</v>
       </c>
       <c r="K52" t="n">
-        <v>315000</v>
+        <v>448000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>202,000</t>
+          <t>-76,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3403,48 +3403,48 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>439360</v>
+        <v>113000</v>
       </c>
       <c r="K53" t="n">
-        <v>105360</v>
+        <v>198000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-334,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3466,48 +3466,48 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>5.68%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>5.27%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>13000</v>
+        <v>106000</v>
       </c>
       <c r="K54" t="n">
-        <v>25000</v>
+        <v>99000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3534,22 +3534,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3559,18 +3559,18 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>134000</v>
+        <v>763000</v>
       </c>
       <c r="K55" t="n">
-        <v>107000</v>
+        <v>684000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-27,000</t>
+          <t>-79,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3597,43 +3597,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>149000</v>
+        <v>59000</v>
       </c>
       <c r="K56" t="n">
-        <v>312000</v>
+        <v>131000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3655,48 +3655,48 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>454000</v>
+        <v>102000</v>
       </c>
       <c r="K57" t="n">
-        <v>323000</v>
+        <v>133000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-131,000</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3723,43 +3723,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>97000</v>
+        <v>113000</v>
       </c>
       <c r="K58" t="n">
-        <v>192000</v>
+        <v>315000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>202,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3781,48 +3781,48 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>43000</v>
+        <v>439360</v>
       </c>
       <c r="K59" t="n">
-        <v>88000</v>
+        <v>105360</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>-334,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3849,43 +3849,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>37000</v>
+        <v>13000</v>
       </c>
       <c r="K60" t="n">
-        <v>46000</v>
+        <v>25000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3907,48 +3907,48 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>10000</v>
+        <v>134000</v>
       </c>
       <c r="K61" t="n">
-        <v>22000</v>
+        <v>107000</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>-27,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3970,48 +3970,48 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>304000</v>
+        <v>149000</v>
       </c>
       <c r="K62" t="n">
-        <v>273000</v>
+        <v>312000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4033,48 +4033,48 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>611000</v>
+        <v>454000</v>
       </c>
       <c r="K63" t="n">
-        <v>939000</v>
+        <v>323000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>-131,000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4101,43 +4101,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>367000</v>
+        <v>97000</v>
       </c>
       <c r="K64" t="n">
-        <v>556000</v>
+        <v>192000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>189,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4159,48 +4159,48 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>29000</v>
+        <v>43000</v>
       </c>
       <c r="K65" t="n">
-        <v>23000</v>
+        <v>88000</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4227,43 +4227,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>90000</v>
+        <v>37000</v>
       </c>
       <c r="K66" t="n">
-        <v>100000</v>
+        <v>46000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4290,43 +4290,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>177000</v>
+        <v>10000</v>
       </c>
       <c r="K67" t="n">
-        <v>352000</v>
+        <v>22000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4348,48 +4348,48 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>171000</v>
+        <v>304000</v>
       </c>
       <c r="K68" t="n">
-        <v>390000</v>
+        <v>273000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>219,000</t>
+          <t>-31,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4411,48 +4411,48 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>73872</v>
+        <v>611000</v>
       </c>
       <c r="K69" t="n">
-        <v>52872</v>
+        <v>939000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-21,000</t>
+          <t>328,000</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4479,43 +4479,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>102000</v>
+        <v>367000</v>
       </c>
       <c r="K70" t="n">
-        <v>165000</v>
+        <v>556000</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>189,000</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4537,48 +4537,48 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>173000</v>
+        <v>29000</v>
       </c>
       <c r="K71" t="n">
-        <v>368000</v>
+        <v>23000</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>195,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4600,48 +4600,48 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>115000</v>
+        <v>90000</v>
       </c>
       <c r="K72" t="n">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4668,43 +4668,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>77000</v>
+        <v>177000</v>
       </c>
       <c r="K73" t="n">
-        <v>163000</v>
+        <v>352000</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>86,000</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4726,48 +4726,48 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>249000</v>
+        <v>171000</v>
       </c>
       <c r="K74" t="n">
-        <v>191000</v>
+        <v>390000</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-58,000</t>
+          <t>219,000</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4789,48 +4789,48 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>45000</v>
+        <v>73872</v>
       </c>
       <c r="K75" t="n">
-        <v>90000</v>
+        <v>52872</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>-21,000</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4857,43 +4857,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>47000</v>
+        <v>102000</v>
       </c>
       <c r="K76" t="n">
-        <v>140191</v>
+        <v>165000</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>93,191</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4915,48 +4915,48 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>216000</v>
+        <v>173000</v>
       </c>
       <c r="K77" t="n">
-        <v>185000</v>
+        <v>368000</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>195,000</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -4978,48 +4978,48 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>32000</v>
+        <v>115000</v>
       </c>
       <c r="K78" t="n">
-        <v>67000</v>
+        <v>80000</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5041,48 +5041,48 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>31000</v>
+        <v>77000</v>
       </c>
       <c r="K79" t="n">
-        <v>24000</v>
+        <v>163000</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>86,000</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5104,51 +5104,429 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2.63%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-0.80%</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>249000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>191000</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>-58,000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>45000</v>
+      </c>
+      <c r="K81" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>45,000</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>47000</v>
+      </c>
+      <c r="K82" t="n">
+        <v>140191</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>93,191</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>216000</v>
+      </c>
+      <c r="K83" t="n">
+        <v>185000</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-31,000</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K84" t="n">
+        <v>67000</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>35,000</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K85" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>+0.59%</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="J86" t="n">
         <v>82000</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K86" t="n">
         <v>122000</v>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-03_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-03_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1521,133 +1521,97 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>緯穎科技服務</t>
-        </is>
-      </c>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>緯穎科技服務</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>4.11%</t>
-        </is>
-      </c>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.16%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>56000</v>
-      </c>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>167036</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>111,036</t>
-        </is>
-      </c>
+        <v>158000</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-02_00985A_full_holdings.xlsx</t>
+          <t>2026-09-02_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>7.61%</t>
-        </is>
-      </c>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.69%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-0.92%</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>235000</v>
-      </c>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>205000</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-30,000</t>
-        </is>
-      </c>
+        <v>94000</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-02_00992A_full_holdings.xlsx</t>
+          <t>2026-09-02_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1657,53 +1621,53 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2045000</v>
+        <v>1008000</v>
       </c>
       <c r="K21" t="n">
-        <v>1000000</v>
+        <v>1665000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-1,045,000</t>
+          <t>657,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1720,48 +1684,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>55000</v>
+        <v>2045000</v>
       </c>
       <c r="K22" t="n">
-        <v>80000</v>
+        <v>1000000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>-1,045,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1783,48 +1747,48 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>108000</v>
+        <v>55000</v>
       </c>
       <c r="K23" t="n">
-        <v>54000</v>
+        <v>80000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-54,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1846,48 +1810,48 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2000</v>
+        <v>108000</v>
       </c>
       <c r="K24" t="n">
-        <v>12000</v>
+        <v>54000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>-54,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1914,43 +1878,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>195000</v>
+        <v>2000</v>
       </c>
       <c r="K25" t="n">
-        <v>581644</v>
+        <v>12000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>386,644</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1977,43 +1941,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>5.72%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>5.87%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>221000</v>
+        <v>195000</v>
       </c>
       <c r="K26" t="n">
-        <v>351000</v>
+        <v>581644</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>386,644</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2025,45 +1989,63 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1.72%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>+0.74%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>28000</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+        <v>221000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>351000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2085,24 +2067,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>87000</v>
+        <v>28000</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2130,24 +2112,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>11000</v>
+        <v>87000</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2175,24 +2157,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>29000</v>
+        <v>11000</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2220,24 +2202,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>41000</v>
+        <v>29000</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2265,12 +2247,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>凱基金控</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -2282,7 +2264,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>729000</v>
+        <v>41000</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2310,24 +2292,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>永豐金控</t>
+          <t>凱基金控</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>566220</v>
+        <v>729000</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2355,24 +2337,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>永豐金控</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>16000</v>
+        <v>566220</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2400,24 +2382,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>昇達科技</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>4000</v>
+        <v>16000</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2445,24 +2427,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>100000</v>
+        <v>4000</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2490,24 +2472,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>19000</v>
+        <v>100000</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2535,24 +2517,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>39000</v>
+        <v>19000</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2580,24 +2562,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>33000</v>
+        <v>39000</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2625,24 +2607,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>32000</v>
+        <v>33000</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2670,24 +2652,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>13000</v>
+        <v>32000</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2705,55 +2687,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.83%</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>3.75%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>+1.92%</t>
-        </is>
-      </c>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>821000</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1613000</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>792,000</t>
-        </is>
-      </c>
+        <v>13000</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2773,48 +2737,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>30000</v>
+        <v>821000</v>
       </c>
       <c r="K43" t="n">
-        <v>28000</v>
+        <v>1613000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>792,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -2841,43 +2805,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>3.80%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1338000</v>
+        <v>30000</v>
       </c>
       <c r="K44" t="n">
-        <v>1276000</v>
+        <v>28000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-62,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -2899,48 +2863,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>110000</v>
+        <v>1338000</v>
       </c>
       <c r="K45" t="n">
-        <v>114000</v>
+        <v>1276000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>-62,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -2967,43 +2931,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>78000</v>
+        <v>110000</v>
       </c>
       <c r="K46" t="n">
-        <v>161000</v>
+        <v>114000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>83,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3025,48 +2989,48 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>202000</v>
+        <v>78000</v>
       </c>
       <c r="K47" t="n">
-        <v>167000</v>
+        <v>161000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>83,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3093,43 +3057,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8.39%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7.98%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>363000</v>
+        <v>202000</v>
       </c>
       <c r="K48" t="n">
-        <v>341000</v>
+        <v>167000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-22,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3151,48 +3115,48 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>8.39%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>7.98%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>550000</v>
+        <v>363000</v>
       </c>
       <c r="K49" t="n">
-        <v>629000</v>
+        <v>341000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>-22,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3214,48 +3178,48 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>1496000</v>
+        <v>550000</v>
       </c>
       <c r="K50" t="n">
-        <v>1262000</v>
+        <v>629000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-234,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3282,43 +3246,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>140000</v>
+        <v>1496000</v>
       </c>
       <c r="K51" t="n">
-        <v>138000</v>
+        <v>1262000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-234,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3345,27 +3309,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3374,14 +3338,14 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>524000</v>
+        <v>140000</v>
       </c>
       <c r="K52" t="n">
-        <v>448000</v>
+        <v>138000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-76,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3403,48 +3367,48 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>113000</v>
+        <v>524000</v>
       </c>
       <c r="K53" t="n">
-        <v>198000</v>
+        <v>448000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>-76,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3466,48 +3430,48 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5.27%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>106000</v>
+        <v>113000</v>
       </c>
       <c r="K54" t="n">
-        <v>99000</v>
+        <v>198000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3534,43 +3498,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>5.68%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>5.27%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>763000</v>
+        <v>106000</v>
       </c>
       <c r="K55" t="n">
-        <v>684000</v>
+        <v>99000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-79,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3592,48 +3556,48 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>59000</v>
+        <v>763000</v>
       </c>
       <c r="K56" t="n">
-        <v>131000</v>
+        <v>684000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>-79,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3660,43 +3624,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>102000</v>
+        <v>59000</v>
       </c>
       <c r="K57" t="n">
-        <v>133000</v>
+        <v>131000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3723,43 +3687,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>113000</v>
+        <v>102000</v>
       </c>
       <c r="K58" t="n">
-        <v>315000</v>
+        <v>133000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>202,000</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3781,48 +3745,48 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>439360</v>
+        <v>113000</v>
       </c>
       <c r="K59" t="n">
-        <v>105360</v>
+        <v>315000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-334,000</t>
+          <t>202,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3844,48 +3808,48 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>13000</v>
+        <v>439360</v>
       </c>
       <c r="K60" t="n">
-        <v>25000</v>
+        <v>105360</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>-334,000</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3907,48 +3871,48 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>134000</v>
+        <v>13000</v>
       </c>
       <c r="K61" t="n">
-        <v>107000</v>
+        <v>25000</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-27,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3970,48 +3934,48 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>149000</v>
+        <v>134000</v>
       </c>
       <c r="K62" t="n">
-        <v>312000</v>
+        <v>107000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>-27,000</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4033,48 +3997,48 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>454000</v>
+        <v>149000</v>
       </c>
       <c r="K63" t="n">
-        <v>323000</v>
+        <v>312000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-131,000</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4096,48 +4060,48 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>97000</v>
+        <v>454000</v>
       </c>
       <c r="K64" t="n">
-        <v>192000</v>
+        <v>323000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>-131,000</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4164,43 +4128,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>43000</v>
+        <v>97000</v>
       </c>
       <c r="K65" t="n">
-        <v>88000</v>
+        <v>192000</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4227,43 +4191,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>37000</v>
+        <v>43000</v>
       </c>
       <c r="K66" t="n">
-        <v>46000</v>
+        <v>88000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4290,43 +4254,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>10000</v>
+        <v>37000</v>
       </c>
       <c r="K67" t="n">
-        <v>22000</v>
+        <v>46000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4348,48 +4312,48 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>304000</v>
+        <v>10000</v>
       </c>
       <c r="K68" t="n">
-        <v>273000</v>
+        <v>22000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4411,48 +4375,48 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>611000</v>
+        <v>304000</v>
       </c>
       <c r="K69" t="n">
-        <v>939000</v>
+        <v>273000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>-31,000</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4479,43 +4443,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>367000</v>
+        <v>611000</v>
       </c>
       <c r="K70" t="n">
-        <v>556000</v>
+        <v>939000</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>189,000</t>
+          <t>328,000</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4537,48 +4501,48 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>29000</v>
+        <v>367000</v>
       </c>
       <c r="K71" t="n">
-        <v>23000</v>
+        <v>556000</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>189,000</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4600,48 +4564,48 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>90000</v>
+        <v>29000</v>
       </c>
       <c r="K72" t="n">
-        <v>100000</v>
+        <v>23000</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4668,43 +4632,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>177000</v>
+        <v>90000</v>
       </c>
       <c r="K73" t="n">
-        <v>352000</v>
+        <v>100000</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4731,43 +4695,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>171000</v>
+        <v>177000</v>
       </c>
       <c r="K74" t="n">
-        <v>390000</v>
+        <v>352000</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>219,000</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4789,48 +4753,48 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>73872</v>
+        <v>171000</v>
       </c>
       <c r="K75" t="n">
-        <v>52872</v>
+        <v>390000</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-21,000</t>
+          <t>219,000</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4852,48 +4816,48 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>102000</v>
+        <v>73872</v>
       </c>
       <c r="K76" t="n">
-        <v>165000</v>
+        <v>52872</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>-21,000</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4920,43 +4884,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>173000</v>
+        <v>102000</v>
       </c>
       <c r="K77" t="n">
-        <v>368000</v>
+        <v>165000</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>195,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -4978,48 +4942,48 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>115000</v>
+        <v>173000</v>
       </c>
       <c r="K78" t="n">
-        <v>80000</v>
+        <v>368000</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>195,000</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5041,48 +5005,48 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>77000</v>
+        <v>115000</v>
       </c>
       <c r="K79" t="n">
-        <v>163000</v>
+        <v>80000</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>86,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5104,48 +5068,48 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>249000</v>
+        <v>77000</v>
       </c>
       <c r="K80" t="n">
-        <v>191000</v>
+        <v>163000</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-58,000</t>
+          <t>86,000</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5167,48 +5131,48 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>2.63%</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>45000</v>
+        <v>249000</v>
       </c>
       <c r="K81" t="n">
-        <v>90000</v>
+        <v>191000</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>-58,000</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5235,43 +5199,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>47000</v>
+        <v>45000</v>
       </c>
       <c r="K82" t="n">
-        <v>140191</v>
+        <v>90000</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>93,191</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -5293,48 +5257,48 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>216000</v>
+        <v>47000</v>
       </c>
       <c r="K83" t="n">
-        <v>185000</v>
+        <v>140191</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>93,191</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5356,48 +5320,48 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>32000</v>
+        <v>216000</v>
       </c>
       <c r="K84" t="n">
-        <v>67000</v>
+        <v>185000</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>-31,000</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5419,48 +5383,48 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>勤誠興業</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>勤誠興業</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>0.63%</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>0.48%</t>
-        </is>
-      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="K85" t="n">
-        <v>24000</v>
+        <v>67000</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -5482,51 +5446,114 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K86" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>+0.59%</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="J87" t="n">
         <v>82000</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K87" t="n">
         <v>122000</v>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-03_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-03_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,52 +1098,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>4.11%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.16%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
       <c r="J12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+        <v>56000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>167036</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>111,036</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+          <t>2026-09-02_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1153,186 +1171,150 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>7.61%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>6.69%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1000</v>
+        <v>235000</v>
       </c>
       <c r="K13" t="n">
-        <v>1351000</v>
+        <v>205000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1,350,000</t>
+          <t>-30,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+          <t>2026-09-02_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0.08%</t>
-        </is>
-      </c>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.29%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>1200000</v>
-      </c>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2,800,000</t>
-        </is>
-      </c>
+        <v>158000</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+          <t>2026-09-02_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4966</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>譜瑞-KY</t>
-        </is>
-      </c>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.08%</t>
-        </is>
-      </c>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>220000</v>
-      </c>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>16000</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-204,000</t>
-        </is>
-      </c>
+        <v>94000</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+          <t>2026-09-02_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1347,55 +1329,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>189500</v>
+        <v>1008000</v>
       </c>
       <c r="K16" t="n">
-        <v>210500</v>
+        <v>1665000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>657,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+          <t>2026-09-02_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1405,60 +1387,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>225000</v>
+        <v>2045000</v>
       </c>
       <c r="K17" t="n">
-        <v>350000</v>
+        <v>1000000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>125,000</t>
+          <t>-1,045,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1468,150 +1450,186 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>850000</v>
+        <v>55000</v>
       </c>
       <c r="K18" t="n">
-        <v>650000</v>
+        <v>80000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-200,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-02_00403A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.49%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.57%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>108000</v>
+      </c>
       <c r="K19" t="n">
-        <v>158000</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>54000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-54,000</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-02_00990A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2000</v>
+      </c>
       <c r="K20" t="n">
-        <v>94000</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-02_00990A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1626,48 +1644,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>5.72%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>5.87%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1008000</v>
+        <v>195000</v>
       </c>
       <c r="K21" t="n">
-        <v>1665000</v>
+        <v>581644</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>657,000</t>
+          <t>386,644</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-02_00990A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1684,48 +1702,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2045000</v>
+        <v>221000</v>
       </c>
       <c r="K22" t="n">
-        <v>1000000</v>
+        <v>351000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-1,045,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1737,315 +1755,225 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.57%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2.42%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>+0.85%</t>
-        </is>
-      </c>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>55000</v>
-      </c>
-      <c r="K23" t="n">
-        <v>80000</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>25,000</t>
-        </is>
-      </c>
+        <v>28000</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>力旺</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>力旺</t>
-        </is>
-      </c>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.07%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-0.57%</t>
-        </is>
-      </c>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>108000</v>
-      </c>
-      <c r="K24" t="n">
-        <v>54000</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-54,000</t>
-        </is>
-      </c>
+        <v>87000</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>精測</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>+0.14%</t>
-        </is>
-      </c>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K25" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
+        <v>11000</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5.72%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>5.87%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>+0.15%</t>
-        </is>
-      </c>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>195000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>581644</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>386,644</t>
-        </is>
-      </c>
+        <v>29000</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.98%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1.72%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>+0.74%</t>
-        </is>
-      </c>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>221000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>351000</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>130,000</t>
-        </is>
-      </c>
+        <v>41000</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2067,24 +1995,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>凱基金控</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>28000</v>
+        <v>729000</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2112,24 +2040,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>永豐金控</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>87000</v>
+        <v>566220</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2157,24 +2085,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>昇達科技</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2202,24 +2130,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>29000</v>
+        <v>4000</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2247,24 +2175,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>41000</v>
+        <v>100000</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2292,24 +2220,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>凱基金控</t>
+          <t>萬潤科技</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>729000</v>
+        <v>19000</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2337,24 +2265,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>永豐金控</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>566220</v>
+        <v>39000</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2382,24 +2310,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>16000</v>
+        <v>33000</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2427,24 +2355,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>4000</v>
+        <v>32000</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2472,24 +2400,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>100000</v>
+        <v>13000</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2507,37 +2435,55 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>+1.92%</t>
+        </is>
+      </c>
       <c r="J38" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+        <v>821000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1613000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>792,000</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2552,37 +2498,55 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>帆宣</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+          <t>4.04%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3.80%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
       <c r="J39" t="n">
-        <v>39000</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+        <v>30000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>28000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2597,37 +2561,55 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>聯茂</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
       <c r="J40" t="n">
-        <v>33000</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+        <v>1338000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1276000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-62,000</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2642,37 +2624,55 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>南俊國際</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>台達電子</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>台達電子</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
       <c r="J41" t="n">
-        <v>32000</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+        <v>110000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2687,37 +2687,55 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.73%</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>+0.20%</t>
+        </is>
+      </c>
       <c r="J42" t="n">
-        <v>13000</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+        <v>78000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>161000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>83,000</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2737,48 +2755,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>821000</v>
+        <v>202000</v>
       </c>
       <c r="K43" t="n">
-        <v>1613000</v>
+        <v>167000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>792,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -2805,43 +2823,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>8.39%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>7.98%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>30000</v>
+        <v>363000</v>
       </c>
       <c r="K44" t="n">
-        <v>28000</v>
+        <v>341000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-22,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -2863,48 +2881,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>1338000</v>
+        <v>550000</v>
       </c>
       <c r="K45" t="n">
-        <v>1276000</v>
+        <v>629000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-62,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -2926,48 +2944,48 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>台達電子</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>110000</v>
+        <v>1496000</v>
       </c>
       <c r="K46" t="n">
-        <v>114000</v>
+        <v>1262000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>-234,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -2989,48 +3007,48 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>78000</v>
+        <v>140000</v>
       </c>
       <c r="K47" t="n">
-        <v>161000</v>
+        <v>138000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>83,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3057,43 +3075,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>202000</v>
+        <v>524000</v>
       </c>
       <c r="K48" t="n">
-        <v>167000</v>
+        <v>448000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>-76,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3115,48 +3133,48 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8.39%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>7.98%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>363000</v>
+        <v>113000</v>
       </c>
       <c r="K49" t="n">
-        <v>341000</v>
+        <v>198000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-22,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3178,48 +3196,48 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>5.68%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>5.27%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>550000</v>
+        <v>106000</v>
       </c>
       <c r="K50" t="n">
-        <v>629000</v>
+        <v>99000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3246,43 +3264,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1496000</v>
+        <v>763000</v>
       </c>
       <c r="K51" t="n">
-        <v>1262000</v>
+        <v>684000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-234,000</t>
+          <t>-79,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3304,48 +3322,48 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>140000</v>
+        <v>59000</v>
       </c>
       <c r="K52" t="n">
-        <v>138000</v>
+        <v>131000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3367,48 +3385,48 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>524000</v>
+        <v>102000</v>
       </c>
       <c r="K53" t="n">
-        <v>448000</v>
+        <v>133000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-76,000</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3435,43 +3453,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="J54" t="n">
         <v>113000</v>
       </c>
       <c r="K54" t="n">
-        <v>198000</v>
+        <v>315000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>202,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3498,43 +3516,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5.27%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>106000</v>
+        <v>439360</v>
       </c>
       <c r="K55" t="n">
-        <v>99000</v>
+        <v>105360</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>-334,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3556,48 +3574,48 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>763000</v>
+        <v>13000</v>
       </c>
       <c r="K56" t="n">
-        <v>684000</v>
+        <v>25000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-79,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3619,48 +3637,48 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>59000</v>
+        <v>134000</v>
       </c>
       <c r="K57" t="n">
-        <v>131000</v>
+        <v>107000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>-27,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3687,43 +3705,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>102000</v>
+        <v>149000</v>
       </c>
       <c r="K58" t="n">
-        <v>133000</v>
+        <v>312000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3745,48 +3763,48 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>113000</v>
+        <v>454000</v>
       </c>
       <c r="K59" t="n">
-        <v>315000</v>
+        <v>323000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>202,000</t>
+          <t>-131,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3808,48 +3826,48 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>439360</v>
+        <v>97000</v>
       </c>
       <c r="K60" t="n">
-        <v>105360</v>
+        <v>192000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-334,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3876,43 +3894,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>13000</v>
+        <v>43000</v>
       </c>
       <c r="K61" t="n">
-        <v>25000</v>
+        <v>88000</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3934,48 +3952,48 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>134000</v>
+        <v>37000</v>
       </c>
       <c r="K62" t="n">
-        <v>107000</v>
+        <v>46000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-27,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4002,43 +4020,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>149000</v>
+        <v>10000</v>
       </c>
       <c r="K63" t="n">
-        <v>312000</v>
+        <v>22000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4065,43 +4083,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>454000</v>
+        <v>304000</v>
       </c>
       <c r="K64" t="n">
-        <v>323000</v>
+        <v>273000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-131,000</t>
+          <t>-31,000</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4128,43 +4146,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>97000</v>
+        <v>611000</v>
       </c>
       <c r="K65" t="n">
-        <v>192000</v>
+        <v>939000</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>328,000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4191,43 +4209,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>43000</v>
+        <v>367000</v>
       </c>
       <c r="K66" t="n">
-        <v>88000</v>
+        <v>556000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>189,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4249,48 +4267,48 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>37000</v>
+        <v>29000</v>
       </c>
       <c r="K67" t="n">
-        <v>46000</v>
+        <v>23000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4317,43 +4335,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>10000</v>
+        <v>90000</v>
       </c>
       <c r="K68" t="n">
-        <v>22000</v>
+        <v>100000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4375,48 +4393,48 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>304000</v>
+        <v>177000</v>
       </c>
       <c r="K69" t="n">
-        <v>273000</v>
+        <v>352000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4443,43 +4461,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>611000</v>
+        <v>171000</v>
       </c>
       <c r="K70" t="n">
-        <v>939000</v>
+        <v>390000</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>219,000</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4501,48 +4519,48 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>367000</v>
+        <v>73872</v>
       </c>
       <c r="K71" t="n">
-        <v>556000</v>
+        <v>52872</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>189,000</t>
+          <t>-21,000</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4564,48 +4582,48 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>29000</v>
+        <v>102000</v>
       </c>
       <c r="K72" t="n">
-        <v>23000</v>
+        <v>165000</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4632,43 +4650,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>90000</v>
+        <v>173000</v>
       </c>
       <c r="K73" t="n">
-        <v>100000</v>
+        <v>368000</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>195,000</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4690,48 +4708,48 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>177000</v>
+        <v>115000</v>
       </c>
       <c r="K74" t="n">
-        <v>352000</v>
+        <v>80000</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4758,43 +4776,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>171000</v>
+        <v>77000</v>
       </c>
       <c r="K75" t="n">
-        <v>390000</v>
+        <v>163000</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>219,000</t>
+          <t>86,000</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4821,43 +4839,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>2.63%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>73872</v>
+        <v>249000</v>
       </c>
       <c r="K76" t="n">
-        <v>52872</v>
+        <v>191000</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-21,000</t>
+          <t>-58,000</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4884,43 +4902,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>102000</v>
+        <v>45000</v>
       </c>
       <c r="K77" t="n">
-        <v>165000</v>
+        <v>90000</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -4947,43 +4965,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>173000</v>
+        <v>47000</v>
       </c>
       <c r="K78" t="n">
-        <v>368000</v>
+        <v>140191</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>195,000</t>
+          <t>93,191</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5010,43 +5028,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>115000</v>
+        <v>216000</v>
       </c>
       <c r="K79" t="n">
-        <v>80000</v>
+        <v>185000</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>-31,000</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5073,43 +5091,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>勤誠興業</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>勤誠興業</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>77000</v>
+        <v>32000</v>
       </c>
       <c r="K80" t="n">
-        <v>163000</v>
+        <v>67000</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>86,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5136,43 +5154,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>群聯電子</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>群聯電子</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>249000</v>
+        <v>31000</v>
       </c>
       <c r="K81" t="n">
-        <v>191000</v>
+        <v>24000</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-58,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5199,361 +5217,46 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.59%</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>45000</v>
+        <v>82000</v>
       </c>
       <c r="K82" t="n">
-        <v>90000</v>
+        <v>122000</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
-        <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>3.49%</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>3.58%</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>47000</v>
-      </c>
-      <c r="K83" t="n">
-        <v>140191</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>93,191</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2.52%</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>2.17%</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-0.35%</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>216000</v>
-      </c>
-      <c r="K84" t="n">
-        <v>185000</v>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>-31,000</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>勤誠興業</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>勤誠興業</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>+0.33%</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>32000</v>
-      </c>
-      <c r="K85" t="n">
-        <v>67000</v>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>35,000</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>0.48%</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-0.15%</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>31000</v>
-      </c>
-      <c r="K86" t="n">
-        <v>24000</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-7,000</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>0.92%</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>1.51%</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>+0.59%</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>82000</v>
-      </c>
-      <c r="K87" t="n">
-        <v>122000</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-03_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-03_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,70 +1098,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>緯穎科技服務</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>緯穎科技服務</t>
-        </is>
-      </c>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.11%</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4.16%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>56000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>167036</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>111,036</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-02_00985A_full_holdings.xlsx</t>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1171,150 +1153,186 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6.69%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>235000</v>
+        <v>1000</v>
       </c>
       <c r="K13" t="n">
-        <v>205000</v>
+        <v>1351000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-30,000</t>
+          <t>1,350,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-02_00992A_full_holdings.xlsx</t>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.49%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1200000</v>
+      </c>
       <c r="K14" t="n">
-        <v>158000</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>4000000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2,800,000</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-02_00990A_full_holdings.xlsx</t>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>220000</v>
+      </c>
       <c r="K15" t="n">
-        <v>94000</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>16000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-204,000</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-02_00990A_full_holdings.xlsx</t>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1329,55 +1347,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1008000</v>
+        <v>189500</v>
       </c>
       <c r="K16" t="n">
-        <v>1665000</v>
+        <v>210500</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>657,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-02_00990A_full_holdings.xlsx</t>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1387,60 +1405,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2045000</v>
+        <v>225000</v>
       </c>
       <c r="K17" t="n">
-        <v>1000000</v>
+        <v>350000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-1,045,000</t>
+          <t>125,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1450,60 +1468,60 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>55000</v>
+        <v>850000</v>
       </c>
       <c r="K18" t="n">
-        <v>80000</v>
+        <v>650000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1513,60 +1531,60 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>緯穎科技服務</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>緯穎科技服務</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>4.16%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>108000</v>
+        <v>56000</v>
       </c>
       <c r="K19" t="n">
-        <v>54000</v>
+        <v>167036</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-54,000</t>
+          <t>111,036</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1576,494 +1594,584 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>7.61%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>6.69%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2000</v>
+        <v>235000</v>
       </c>
       <c r="K20" t="n">
-        <v>12000</v>
+        <v>205000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>-30,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>5.72%</t>
-        </is>
-      </c>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.87%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>+0.15%</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>195000</v>
-      </c>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>581644</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>386,644</t>
-        </is>
-      </c>
+        <v>158000</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.98%</t>
-        </is>
-      </c>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.72%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>+0.74%</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>221000</v>
-      </c>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>351000</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>130,000</t>
-        </is>
-      </c>
+        <v>94000</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-02_00407A_full_holdings.xlsx</t>
+          <t>2026-09-02_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>+0.58%</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>28000</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+        <v>1008000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1665000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>657,000</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>光寶科技</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.53%</t>
+        </is>
+      </c>
       <c r="J24" t="n">
-        <v>87000</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+        <v>2045000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-1,045,000</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>11000</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+        <v>55000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>80000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-0.57%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>29000</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+        <v>108000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>54000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-54,000</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>志聖</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>41000</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>凱基金控</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+          <t>5.72%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5.87%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
       <c r="J28" t="n">
-        <v>729000</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+        <v>195000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>581644</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>386,644</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>永豐金控</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.22%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1.72%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+0.74%</t>
+        </is>
+      </c>
       <c r="J29" t="n">
-        <v>566220</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+        <v>221000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>351000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+          <t>2026-09-02_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2085,24 +2193,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>16000</v>
+        <v>28000</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2130,24 +2238,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>4000</v>
+        <v>87000</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2175,24 +2283,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>100000</v>
+        <v>11000</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2220,24 +2328,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>19000</v>
+        <v>29000</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2265,24 +2373,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>39000</v>
+        <v>41000</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2310,24 +2418,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>凱基金控</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>33000</v>
+        <v>729000</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2355,24 +2463,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>永豐金控</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>32000</v>
+        <v>566220</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2400,24 +2508,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>昇達科技</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>13000</v>
+        <v>16000</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2435,55 +2543,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.83%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>3.75%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>+1.92%</t>
-        </is>
-      </c>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>821000</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1613000</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>792,000</t>
-        </is>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2498,55 +2588,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.04%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>3.80%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
-        </is>
-      </c>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K39" t="n">
-        <v>28000</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2561,55 +2633,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.69%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>1.57%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-0.12%</t>
-        </is>
-      </c>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>1338000</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1276000</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>-62,000</t>
-        </is>
-      </c>
+        <v>19000</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2624,55 +2678,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>台達電子</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>台達電子</t>
-        </is>
-      </c>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>1.93%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>110000</v>
-      </c>
-      <c r="K41" t="n">
-        <v>114000</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
+        <v>39000</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2687,55 +2723,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>+0.20%</t>
-        </is>
-      </c>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>78000</v>
-      </c>
-      <c r="K42" t="n">
-        <v>161000</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>83,000</t>
-        </is>
-      </c>
+        <v>33000</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2750,55 +2768,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.09%</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.88%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>202000</v>
-      </c>
-      <c r="K43" t="n">
-        <v>167000</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-35,000</t>
-        </is>
-      </c>
+        <v>32000</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2813,55 +2813,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>8.39%</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>7.98%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>363000</v>
-      </c>
-      <c r="K44" t="n">
-        <v>341000</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>-22,000</t>
-        </is>
-      </c>
+        <v>13000</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
@@ -2886,43 +2868,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>550000</v>
+        <v>821000</v>
       </c>
       <c r="K45" t="n">
-        <v>629000</v>
+        <v>1613000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>792,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -2949,43 +2931,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>3.80%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>1496000</v>
+        <v>30000</v>
       </c>
       <c r="K46" t="n">
-        <v>1262000</v>
+        <v>28000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-234,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3012,43 +2994,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>140000</v>
+        <v>1338000</v>
       </c>
       <c r="K47" t="n">
-        <v>138000</v>
+        <v>1276000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-62,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3070,48 +3052,48 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>台達電子</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>524000</v>
+        <v>110000</v>
       </c>
       <c r="K48" t="n">
-        <v>448000</v>
+        <v>114000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-76,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3138,43 +3120,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>金像電子</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>113000</v>
+        <v>78000</v>
       </c>
       <c r="K49" t="n">
-        <v>198000</v>
+        <v>161000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>83,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3201,43 +3183,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5.27%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>106000</v>
+        <v>202000</v>
       </c>
       <c r="K50" t="n">
-        <v>99000</v>
+        <v>167000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3264,43 +3246,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>8.39%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>7.98%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>763000</v>
+        <v>363000</v>
       </c>
       <c r="K51" t="n">
-        <v>684000</v>
+        <v>341000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-79,000</t>
+          <t>-22,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3327,43 +3309,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>59000</v>
+        <v>550000</v>
       </c>
       <c r="K52" t="n">
-        <v>131000</v>
+        <v>629000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>72,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3385,48 +3367,48 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>102000</v>
+        <v>1496000</v>
       </c>
       <c r="K53" t="n">
-        <v>133000</v>
+        <v>1262000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>-234,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3448,48 +3430,48 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>113000</v>
+        <v>140000</v>
       </c>
       <c r="K54" t="n">
-        <v>315000</v>
+        <v>138000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>202,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3516,43 +3498,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>439360</v>
+        <v>524000</v>
       </c>
       <c r="K55" t="n">
-        <v>105360</v>
+        <v>448000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-334,000</t>
+          <t>-76,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3579,43 +3561,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>金像電子</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>13000</v>
+        <v>113000</v>
       </c>
       <c r="K56" t="n">
-        <v>25000</v>
+        <v>198000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3642,43 +3624,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>5.68%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>5.27%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>134000</v>
+        <v>106000</v>
       </c>
       <c r="K57" t="n">
-        <v>107000</v>
+        <v>99000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-27,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3700,48 +3682,48 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>149000</v>
+        <v>763000</v>
       </c>
       <c r="K58" t="n">
-        <v>312000</v>
+        <v>684000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>-79,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3763,48 +3745,48 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>454000</v>
+        <v>59000</v>
       </c>
       <c r="K59" t="n">
-        <v>323000</v>
+        <v>131000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-131,000</t>
+          <t>72,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3831,43 +3813,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>97000</v>
+        <v>102000</v>
       </c>
       <c r="K60" t="n">
-        <v>192000</v>
+        <v>133000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3894,43 +3876,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>43000</v>
+        <v>113000</v>
       </c>
       <c r="K61" t="n">
-        <v>88000</v>
+        <v>315000</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>202,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -3952,48 +3934,48 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>聯亞光電</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>37000</v>
+        <v>439360</v>
       </c>
       <c r="K62" t="n">
-        <v>46000</v>
+        <v>105360</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>-334,000</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4020,39 +4002,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="K63" t="n">
-        <v>22000</v>
+        <v>25000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -4083,43 +4065,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>304000</v>
+        <v>134000</v>
       </c>
       <c r="K64" t="n">
-        <v>273000</v>
+        <v>107000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>-27,000</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4146,43 +4128,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>611000</v>
+        <v>149000</v>
       </c>
       <c r="K65" t="n">
-        <v>939000</v>
+        <v>312000</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4204,48 +4186,48 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>367000</v>
+        <v>454000</v>
       </c>
       <c r="K66" t="n">
-        <v>556000</v>
+        <v>323000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>189,000</t>
+          <t>-131,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4267,48 +4249,48 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>29000</v>
+        <v>97000</v>
       </c>
       <c r="K67" t="n">
-        <v>23000</v>
+        <v>192000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4335,43 +4317,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>90000</v>
+        <v>43000</v>
       </c>
       <c r="K68" t="n">
-        <v>100000</v>
+        <v>88000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4398,43 +4380,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>聯亞光電</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>177000</v>
+        <v>37000</v>
       </c>
       <c r="K69" t="n">
-        <v>352000</v>
+        <v>46000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4461,43 +4443,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>171000</v>
+        <v>10000</v>
       </c>
       <c r="K70" t="n">
-        <v>390000</v>
+        <v>22000</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>219,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4524,43 +4506,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>宜鼎國際</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>73872</v>
+        <v>304000</v>
       </c>
       <c r="K71" t="n">
-        <v>52872</v>
+        <v>273000</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-21,000</t>
+          <t>-31,000</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4587,43 +4569,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>102000</v>
+        <v>611000</v>
       </c>
       <c r="K72" t="n">
-        <v>165000</v>
+        <v>939000</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>328,000</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4650,43 +4632,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>173000</v>
+        <v>367000</v>
       </c>
       <c r="K73" t="n">
-        <v>368000</v>
+        <v>556000</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>195,000</t>
+          <t>189,000</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4713,43 +4695,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>115000</v>
+        <v>29000</v>
       </c>
       <c r="K74" t="n">
-        <v>80000</v>
+        <v>23000</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4776,43 +4758,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>77000</v>
+        <v>90000</v>
       </c>
       <c r="K75" t="n">
-        <v>163000</v>
+        <v>100000</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>86,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4834,48 +4816,48 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-0.80%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>249000</v>
+        <v>177000</v>
       </c>
       <c r="K76" t="n">
-        <v>191000</v>
+        <v>352000</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-58,000</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4902,43 +4884,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>45000</v>
+        <v>171000</v>
       </c>
       <c r="K77" t="n">
-        <v>90000</v>
+        <v>390000</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>219,000</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -4960,48 +4942,48 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>宜鼎國際</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>47000</v>
+        <v>73872</v>
       </c>
       <c r="K78" t="n">
-        <v>140191</v>
+        <v>52872</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>93,191</t>
+          <t>-21,000</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5023,48 +5005,48 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>216000</v>
+        <v>102000</v>
       </c>
       <c r="K79" t="n">
-        <v>185000</v>
+        <v>165000</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-31,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5091,17 +5073,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>勤誠興業</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5111,23 +5093,23 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>32000</v>
+        <v>173000</v>
       </c>
       <c r="K80" t="n">
-        <v>67000</v>
+        <v>368000</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>195,000</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5154,43 +5136,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>31000</v>
+        <v>115000</v>
       </c>
       <c r="K81" t="n">
-        <v>24000</v>
+        <v>80000</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5217,46 +5199,487 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>77000</v>
+      </c>
+      <c r="K82" t="n">
+        <v>163000</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>86,000</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2.63%</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-0.80%</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>249000</v>
+      </c>
+      <c r="K83" t="n">
+        <v>191000</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-58,000</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>45000</v>
+      </c>
+      <c r="K84" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>45,000</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>47000</v>
+      </c>
+      <c r="K85" t="n">
+        <v>140191</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>93,191</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>216000</v>
+      </c>
+      <c r="K86" t="n">
+        <v>185000</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-31,000</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K87" t="n">
+        <v>67000</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>35,000</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K88" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-02_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>+0.59%</t>
         </is>
       </c>
-      <c r="J82" t="n">
+      <c r="J89" t="n">
         <v>82000</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K89" t="n">
         <v>122000</v>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>2026-09-02_00993A_full_holdings.xlsx</t>
         </is>
